--- a/data/output/exports/eneve_full_199_dashboard.xlsx
+++ b/data/output/exports/eneve_full_199_dashboard.xlsx
@@ -697,7 +697,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2026-03-01 19:48</t>
+          <t>2026-03-01 20:08</t>
         </is>
       </c>
     </row>
